--- a/PCB/PicknPlace.xlsx
+++ b/PCB/PicknPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_OXFP_2025-06-25" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_OXFP_2025-08-18" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="71">
   <si>
     <t>Designator</t>
   </si>
@@ -94,19 +94,76 @@
     <t>-23.731mm</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>RGB1</t>
+  </si>
+  <si>
+    <t>WS2812</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L5.0-W5.0-TL-A</t>
+  </si>
+  <si>
+    <t>11.811mm</t>
+  </si>
+  <si>
+    <t>-16.129mm</t>
+  </si>
+  <si>
+    <t>10.211mm</t>
+  </si>
+  <si>
+    <t>-18.479mm</t>
+  </si>
+  <si>
     <t>T</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Eject</t>
-  </si>
-  <si>
-    <t>B3F-1000</t>
-  </si>
-  <si>
-    <t>KEY-TH_4P-L6.2-W6.2-P4.50-LS6.5</t>
+    <t>RGB2</t>
+  </si>
+  <si>
+    <t>64.77mm</t>
+  </si>
+  <si>
+    <t>-15.367mm</t>
+  </si>
+  <si>
+    <t>63.17mm</t>
+  </si>
+  <si>
+    <t>-17.717mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>ESP32-C6-Zero</t>
+  </si>
+  <si>
+    <t>COMM-SMD_18P-P2.54-L23.5-W18.0-TL</t>
+  </si>
+  <si>
+    <t>-25.908mm</t>
+  </si>
+  <si>
+    <t>-13.335mm</t>
+  </si>
+  <si>
+    <t>-36.068mm</t>
+  </si>
+  <si>
+    <t>-20.955mm</t>
+  </si>
+  <si>
+    <t>EJECT</t>
+  </si>
+  <si>
+    <t>TSC015B07518A02</t>
+  </si>
+  <si>
+    <t>SW-SMD_4P-L4.5-W4.5-P3.00-LS6.8</t>
   </si>
   <si>
     <t>37.338mm</t>
@@ -115,82 +172,58 @@
     <t>-15.494mm</t>
   </si>
   <si>
-    <t>40.589mm</t>
-  </si>
-  <si>
-    <t>-17.744mm</t>
+    <t>34.088mm</t>
+  </si>
+  <si>
+    <t>-13.994mm</t>
   </si>
   <si>
     <t>POWER</t>
   </si>
   <si>
-    <t>37.211mm</t>
-  </si>
-  <si>
-    <t>-36.068mm</t>
-  </si>
-  <si>
-    <t>40.462mm</t>
-  </si>
-  <si>
-    <t>-38.318mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>ESP32-S3-Zero</t>
-  </si>
-  <si>
-    <t>COMM-SMD_18P-P2.54-L23.5-W18.0-TL</t>
-  </si>
-  <si>
-    <t>37.084mm</t>
-  </si>
-  <si>
-    <t>-14.605mm</t>
-  </si>
-  <si>
-    <t>44.704mm</t>
-  </si>
-  <si>
-    <t>-4.445mm</t>
-  </si>
-  <si>
-    <t>RGB1</t>
-  </si>
-  <si>
-    <t>WS2812</t>
-  </si>
-  <si>
-    <t>LED-SMD_4P-L5.0-W5.0-TL-A</t>
-  </si>
-  <si>
-    <t>11.811mm</t>
-  </si>
-  <si>
-    <t>-16.129mm</t>
-  </si>
-  <si>
-    <t>10.211mm</t>
-  </si>
-  <si>
-    <t>-18.479mm</t>
-  </si>
-  <si>
-    <t>RGB2</t>
-  </si>
-  <si>
-    <t>64.77mm</t>
-  </si>
-  <si>
-    <t>-15.367mm</t>
-  </si>
-  <si>
-    <t>63.17mm</t>
-  </si>
-  <si>
-    <t>-17.717mm</t>
+    <t>-34.568mm</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>72.216mm</t>
+  </si>
+  <si>
+    <t>-3.475mm</t>
+  </si>
+  <si>
+    <t>RGBO2</t>
+  </si>
+  <si>
+    <t>SH1.0-3P</t>
+  </si>
+  <si>
+    <t>CONN-SMD_3P-P1.00-L5.0-W5.0</t>
+  </si>
+  <si>
+    <t>-4.826mm</t>
+  </si>
+  <si>
+    <t>-20.574mm</t>
+  </si>
+  <si>
+    <t>-5.826mm</t>
+  </si>
+  <si>
+    <t>-18.624mm</t>
+  </si>
+  <si>
+    <t>RGBO1</t>
+  </si>
+  <si>
+    <t>-6.223mm</t>
+  </si>
+  <si>
+    <t>-3.826mm</t>
+  </si>
+  <si>
+    <t>-8.173mm</t>
   </si>
 </sst>
 </file>
@@ -567,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -693,13 +726,13 @@
         <v>9</v>
       </c>
       <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
         <v>27</v>
-      </c>
-      <c r="L3">
-        <v>180</v>
-      </c>
-      <c r="M3" t="s">
-        <v>28</v>
       </c>
       <c r="N3" t="s">
         <v>22</v>
@@ -707,46 +740,46 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
         <v>33</v>
       </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>34</v>
-      </c>
-      <c r="I4" t="s">
-        <v>35</v>
       </c>
       <c r="J4">
         <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -754,10 +787,10 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>37</v>
@@ -781,16 +814,16 @@
         <v>4</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -825,13 +858,13 @@
         <v>36</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L6">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N6" t="s">
         <v>42</v>
@@ -869,10 +902,10 @@
         <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L7">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>20</v>
@@ -892,37 +925,169 @@
         <v>50</v>
       </c>
       <c r="D8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" t="s">
-        <v>59</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="L8">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M8" t="s">
         <v>20</v>
       </c>
       <c r="N8" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9">
+        <v>180</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10">
+        <v>5</v>
+      </c>
+      <c r="K10" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11">
+        <v>180</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/PCB/PicknPlace.xlsx
+++ b/PCB/PicknPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_OXFP_2025-08-18" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_OXFP_2025-08-22" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
   <si>
     <t>Designator</t>
   </si>
@@ -181,7 +181,16 @@
     <t>POWER</t>
   </si>
   <si>
-    <t>-34.568mm</t>
+    <t>37.719mm</t>
+  </si>
+  <si>
+    <t>-36.449mm</t>
+  </si>
+  <si>
+    <t>34.469mm</t>
+  </si>
+  <si>
+    <t>-34.949mm</t>
   </si>
   <si>
     <t>GND</t>
@@ -925,22 +934,22 @@
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="I8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -960,7 +969,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
@@ -969,22 +978,22 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1004,31 +1013,31 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1043,36 +1052,36 @@
         <v>20</v>
       </c>
       <c r="N10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1087,7 +1096,7 @@
         <v>20</v>
       </c>
       <c r="N11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/PCB/PicknPlace.xlsx
+++ b/PCB/PicknPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_OXFP_2025-08-22" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_OXFP_2025-10-21" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="77">
   <si>
     <t>Designator</t>
   </si>
@@ -233,6 +233,15 @@
   </si>
   <si>
     <t>-8.173mm</t>
+  </si>
+  <si>
+    <t>EJECT_TP</t>
+  </si>
+  <si>
+    <t>71.808mm</t>
+  </si>
+  <si>
+    <t>-21.001mm</t>
   </si>
 </sst>
 </file>
@@ -609,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -1099,6 +1108,50 @@
         <v>64</v>
       </c>
     </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12">
+        <v>180</v>
+      </c>
+      <c r="M12" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
